--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91320</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91373</v>
+        <v>91378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128366410</v>
+        <v>128366426</v>
       </c>
       <c r="B2" t="n">
-        <v>91431</v>
+        <v>91485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730447</v>
+        <v>730469</v>
       </c>
       <c r="R2" t="n">
-        <v>7119414</v>
+        <v>7119424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366426</v>
+        <v>128366410</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730469</v>
+        <v>730447</v>
       </c>
       <c r="R3" t="n">
-        <v>7119424</v>
+        <v>7119414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128366426</v>
+        <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730469</v>
+        <v>730447</v>
       </c>
       <c r="R2" t="n">
-        <v>7119424</v>
+        <v>7119414</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366410</v>
+        <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91432</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730447</v>
+        <v>730469</v>
       </c>
       <c r="R3" t="n">
-        <v>7119414</v>
+        <v>7119424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128366415</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,14 +792,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128366426</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128366410</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,41 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366426</v>
+        <v>128384270</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730469</v>
+        <v>730661</v>
       </c>
       <c r="R3" t="n">
-        <v>7119424</v>
+        <v>7119459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,57 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366415</v>
+        <v>128384274</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730445</v>
+        <v>730603</v>
       </c>
       <c r="R4" t="n">
-        <v>7119430</v>
+        <v>7119553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,15 +954,606 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128384275</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730561</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7119507</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128384246</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730689</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7119410</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128366415</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730445</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7119430</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Elin Kannerby</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128384250</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>730608</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7119552</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128384277</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730689</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7119419</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122742882</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Furuhösen V, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730505</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7119512</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28826-2024 artfynd.xlsx
+++ b/artfynd/A 28826-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384274</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384275</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384246</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366415</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384250</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384277</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,8 +1599,24 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742882</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>